--- a/Supplementary_Tables/Supplementary_Tables.xlsx
+++ b/Supplementary_Tables/Supplementary_Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1780939e69baf969/ColocBoost/Manuscript/WIP_Folder/Apr2025/submission/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="281" documentId="8_{6C3E5AC5-D4EC-164B-9F12-075537A0AB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4B76A48-6A3C-9349-90B3-30337A90AD5A}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="8_{6C3E5AC5-D4EC-164B-9F12-075537A0AB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48699A64-EB4A-4A4C-B2C7-DB1B51F87FEC}"/>
   <bookViews>
     <workbookView xWindow="-3920" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{A65ACE89-A6EF-C741-965D-5F7B8E3759D5}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2899" uniqueCount="1360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2899" uniqueCount="1355">
   <si>
     <t>Analysis</t>
   </si>
@@ -4229,21 +4229,6 @@
   </si>
   <si>
     <t>https://zenodo.org/records/15359024</t>
-  </si>
-  <si>
-    <t>https://zenodo.org/records/15359025</t>
-  </si>
-  <si>
-    <t>https://zenodo.org/records/15359026</t>
-  </si>
-  <si>
-    <t>https://zenodo.org/records/15359027</t>
-  </si>
-  <si>
-    <t>https://zenodo.org/records/15359028</t>
-  </si>
-  <si>
-    <t>https://zenodo.org/records/15359029</t>
   </si>
 </sst>
 </file>
@@ -4678,6 +4663,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4720,9 +4708,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4739,6 +4724,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5091,7 +5080,7 @@
       <c r="B3" s="3" t="s">
         <v>1348</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="40" t="s">
         <v>1354</v>
       </c>
     </row>
@@ -5102,8 +5091,8 @@
       <c r="B4" s="3" t="s">
         <v>1351</v>
       </c>
-      <c r="C4" s="54" t="s">
-        <v>1355</v>
+      <c r="C4" s="40" t="s">
+        <v>1354</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -5113,8 +5102,8 @@
       <c r="B5" s="3" t="s">
         <v>1349</v>
       </c>
-      <c r="C5" s="54" t="s">
-        <v>1356</v>
+      <c r="C5" s="40" t="s">
+        <v>1354</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -5124,8 +5113,8 @@
       <c r="B6" s="3" t="s">
         <v>1350</v>
       </c>
-      <c r="C6" s="54" t="s">
-        <v>1357</v>
+      <c r="C6" s="40" t="s">
+        <v>1354</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -5135,8 +5124,8 @@
       <c r="B7" s="3" t="s">
         <v>1352</v>
       </c>
-      <c r="C7" s="54" t="s">
-        <v>1358</v>
+      <c r="C7" s="40" t="s">
+        <v>1354</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -5146,14 +5135,14 @@
       <c r="B8" s="3" t="s">
         <v>1353</v>
       </c>
-      <c r="C8" s="54" t="s">
-        <v>1359</v>
+      <c r="C8" s="40" t="s">
+        <v>1354</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="54"/>
+      <c r="C9" s="40"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C10" s="3"/>
@@ -5174,7 +5163,11 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{441A1189-32D9-8D48-A922-BCE6803BDE97}"/>
-    <hyperlink ref="C4:C9" r:id="rId2" display="https://zenodo.org/records/15359024" xr:uid="{F5A8B520-E16E-984A-B06B-3B3395261BDC}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{1FE4C102-3E99-3A40-AF1C-1E44A048B6A3}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{572E7100-4E36-0545-8A14-95D177EB5DB8}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{7753E92E-B667-154A-91A1-C73100A09D2F}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{47B6AECF-D9DE-B14B-91BF-035509DF0699}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{AACA78C5-E332-EE4A-811C-ADE947F4A6B8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5186,35 +5179,35 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:20" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>1340</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="53" t="s">
         <v>1341</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B3">
@@ -5299,18 +5292,18 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="53" t="s">
         <v>1342</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B9" s="39">
@@ -5502,28 +5495,28 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="53" t="s">
         <v>1343</v>
       </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="53"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="53"/>
-      <c r="P16" s="53"/>
-      <c r="Q16" s="53"/>
-      <c r="R16" s="53"/>
-      <c r="S16" s="53"/>
-      <c r="T16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="54"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="54"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B17" s="39">
@@ -9043,21 +9036,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>818</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
     </row>
     <row r="2" spans="1:14" s="21" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -13025,7 +13018,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="42" t="s">
         <v>336</v>
       </c>
       <c r="B3" s="14" t="s">
@@ -13039,7 +13032,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="41"/>
+      <c r="A4" s="42"/>
       <c r="B4" s="14" t="s">
         <v>339</v>
       </c>
@@ -13051,7 +13044,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="41"/>
+      <c r="A5" s="42"/>
       <c r="B5" s="14" t="s">
         <v>341</v>
       </c>
@@ -13063,7 +13056,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="41"/>
+      <c r="A6" s="42"/>
       <c r="B6" s="14" t="s">
         <v>343</v>
       </c>
@@ -13075,7 +13068,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A7" s="41"/>
+      <c r="A7" s="42"/>
       <c r="B7" s="14" t="s">
         <v>345</v>
       </c>
@@ -13177,12 +13170,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>916</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
@@ -13199,7 +13192,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="43" t="s">
         <v>823</v>
       </c>
       <c r="B3" s="27" t="s">
@@ -13213,7 +13206,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
+      <c r="A4" s="44"/>
       <c r="B4" s="27" t="s">
         <v>826</v>
       </c>
@@ -13225,7 +13218,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="27" t="s">
         <v>827</v>
       </c>
@@ -13237,7 +13230,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="27" t="s">
         <v>828</v>
       </c>
@@ -13249,7 +13242,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="27" t="s">
         <v>829</v>
       </c>
@@ -13261,7 +13254,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43"/>
+      <c r="A8" s="44"/>
       <c r="B8" s="27" t="s">
         <v>830</v>
       </c>
@@ -13276,7 +13269,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43"/>
+      <c r="A9" s="44"/>
       <c r="B9" s="27" t="s">
         <v>832</v>
       </c>
@@ -13291,7 +13284,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43"/>
+      <c r="A10" s="44"/>
       <c r="B10" s="27" t="s">
         <v>834</v>
       </c>
@@ -13303,7 +13296,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44"/>
+      <c r="A11" s="45"/>
       <c r="B11" s="27" t="s">
         <v>835</v>
       </c>
@@ -13315,7 +13308,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="43" t="s">
         <v>836</v>
       </c>
       <c r="B12" s="27" t="s">
@@ -13329,7 +13322,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43"/>
+      <c r="A13" s="44"/>
       <c r="B13" s="27" t="s">
         <v>838</v>
       </c>
@@ -13341,7 +13334,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43"/>
+      <c r="A14" s="44"/>
       <c r="B14" s="27" t="s">
         <v>839</v>
       </c>
@@ -13353,7 +13346,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="43"/>
+      <c r="A15" s="44"/>
       <c r="B15" s="27" t="s">
         <v>840</v>
       </c>
@@ -13365,7 +13358,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
+      <c r="A16" s="44"/>
       <c r="B16" s="27" t="s">
         <v>841</v>
       </c>
@@ -13377,7 +13370,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
+      <c r="A17" s="45"/>
       <c r="B17" s="27" t="s">
         <v>842</v>
       </c>
@@ -13389,7 +13382,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="43" t="s">
         <v>843</v>
       </c>
       <c r="B18" s="27" t="s">
@@ -13403,7 +13396,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="43"/>
+      <c r="A19" s="44"/>
       <c r="B19" s="27" t="s">
         <v>845</v>
       </c>
@@ -13415,7 +13408,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="43"/>
+      <c r="A20" s="44"/>
       <c r="B20" s="27" t="s">
         <v>846</v>
       </c>
@@ -13427,7 +13420,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="43"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="27" t="s">
         <v>847</v>
       </c>
@@ -13439,7 +13432,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="43"/>
+      <c r="A22" s="44"/>
       <c r="B22" s="27" t="s">
         <v>848</v>
       </c>
@@ -13451,7 +13444,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="43"/>
+      <c r="A23" s="44"/>
       <c r="B23" s="27" t="s">
         <v>849</v>
       </c>
@@ -13463,7 +13456,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="43"/>
+      <c r="A24" s="44"/>
       <c r="B24" s="27" t="s">
         <v>851</v>
       </c>
@@ -13475,7 +13468,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="27" t="s">
         <v>853</v>
       </c>
@@ -13487,7 +13480,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="43"/>
+      <c r="A26" s="44"/>
       <c r="B26" s="27" t="s">
         <v>855</v>
       </c>
@@ -13499,7 +13492,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="43"/>
+      <c r="A27" s="44"/>
       <c r="B27" s="27" t="s">
         <v>857</v>
       </c>
@@ -13511,7 +13504,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="43"/>
+      <c r="A28" s="44"/>
       <c r="B28" s="27" t="s">
         <v>858</v>
       </c>
@@ -13523,7 +13516,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="43"/>
+      <c r="A29" s="44"/>
       <c r="B29" s="27" t="s">
         <v>860</v>
       </c>
@@ -13535,7 +13528,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
+      <c r="A30" s="45"/>
       <c r="B30" s="27" t="s">
         <v>862</v>
       </c>
@@ -13547,7 +13540,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="43" t="s">
         <v>864</v>
       </c>
       <c r="B31" s="27" t="s">
@@ -13561,7 +13554,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="43"/>
+      <c r="A32" s="44"/>
       <c r="B32" s="27" t="s">
         <v>866</v>
       </c>
@@ -13573,7 +13566,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="43"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="27" t="s">
         <v>868</v>
       </c>
@@ -13585,7 +13578,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="43"/>
+      <c r="A34" s="44"/>
       <c r="B34" s="27" t="s">
         <v>870</v>
       </c>
@@ -13597,7 +13590,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="43"/>
+      <c r="A35" s="44"/>
       <c r="B35" s="27" t="s">
         <v>872</v>
       </c>
@@ -13609,7 +13602,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="43"/>
+      <c r="A36" s="44"/>
       <c r="B36" s="27" t="s">
         <v>874</v>
       </c>
@@ -13621,7 +13614,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="43"/>
+      <c r="A37" s="44"/>
       <c r="B37" s="27" t="s">
         <v>875</v>
       </c>
@@ -13633,7 +13626,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="43"/>
+      <c r="A38" s="44"/>
       <c r="B38" s="27" t="s">
         <v>877</v>
       </c>
@@ -13645,7 +13638,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="43"/>
+      <c r="A39" s="44"/>
       <c r="B39" s="27" t="s">
         <v>879</v>
       </c>
@@ -13657,7 +13650,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="43"/>
+      <c r="A40" s="44"/>
       <c r="B40" s="27" t="s">
         <v>880</v>
       </c>
@@ -13669,7 +13662,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="43"/>
+      <c r="A41" s="44"/>
       <c r="B41" s="27" t="s">
         <v>881</v>
       </c>
@@ -13681,7 +13674,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="43"/>
+      <c r="A42" s="44"/>
       <c r="B42" s="27" t="s">
         <v>882</v>
       </c>
@@ -13693,7 +13686,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="43"/>
+      <c r="A43" s="44"/>
       <c r="B43" s="27" t="s">
         <v>883</v>
       </c>
@@ -13705,7 +13698,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="43"/>
+      <c r="A44" s="44"/>
       <c r="B44" s="27" t="s">
         <v>884</v>
       </c>
@@ -13717,7 +13710,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="43"/>
+      <c r="A45" s="44"/>
       <c r="B45" s="27" t="s">
         <v>886</v>
       </c>
@@ -13729,7 +13722,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="43"/>
+      <c r="A46" s="44"/>
       <c r="B46" s="27" t="s">
         <v>888</v>
       </c>
@@ -13741,7 +13734,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="43"/>
+      <c r="A47" s="44"/>
       <c r="B47" s="27" t="s">
         <v>890</v>
       </c>
@@ -13753,7 +13746,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="44"/>
+      <c r="A48" s="45"/>
       <c r="B48" s="27" t="s">
         <v>892</v>
       </c>
@@ -13765,7 +13758,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="42" t="s">
+      <c r="A49" s="43" t="s">
         <v>894</v>
       </c>
       <c r="B49" s="27" t="s">
@@ -13779,7 +13772,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="43"/>
+      <c r="A50" s="44"/>
       <c r="B50" s="27" t="s">
         <v>897</v>
       </c>
@@ -13791,7 +13784,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="43"/>
+      <c r="A51" s="44"/>
       <c r="B51" s="27" t="s">
         <v>899</v>
       </c>
@@ -13803,7 +13796,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="44"/>
+      <c r="A52" s="45"/>
       <c r="B52" s="27" t="s">
         <v>901</v>
       </c>
@@ -13815,7 +13808,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="42" t="s">
+      <c r="A53" s="43" t="s">
         <v>902</v>
       </c>
       <c r="B53" s="27" t="s">
@@ -13829,7 +13822,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="44"/>
+      <c r="A54" s="45"/>
       <c r="B54" s="27" t="s">
         <v>905</v>
       </c>
@@ -13841,7 +13834,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="42" t="s">
+      <c r="A55" s="43" t="s">
         <v>906</v>
       </c>
       <c r="B55" s="27" t="s">
@@ -13855,7 +13848,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="43"/>
+      <c r="A56" s="44"/>
       <c r="B56" s="27" t="s">
         <v>909</v>
       </c>
@@ -13867,7 +13860,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="43"/>
+      <c r="A57" s="44"/>
       <c r="B57" s="27" t="s">
         <v>910</v>
       </c>
@@ -13879,7 +13872,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="43"/>
+      <c r="A58" s="44"/>
       <c r="B58" s="27" t="s">
         <v>911</v>
       </c>
@@ -13891,7 +13884,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="43"/>
+      <c r="A59" s="44"/>
       <c r="B59" s="27" t="s">
         <v>913</v>
       </c>
@@ -13903,7 +13896,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="44"/>
+      <c r="A60" s="45"/>
       <c r="B60" s="27" t="s">
         <v>914</v>
       </c>
@@ -13950,20 +13943,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>1234</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
@@ -19069,20 +19062,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="19" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="48" t="s">
         <v>1336</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
     </row>
     <row r="2" spans="1:12" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31"/>
@@ -19417,20 +19410,20 @@
       <c r="L20" s="31"/>
     </row>
     <row r="21" spans="1:12" ht="19" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="50" t="s">
         <v>1335</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="51"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="2">
